--- a/docs/planning/2026-07-08-OMF-MES-개발-WBS-고객용.xlsx
+++ b/docs/planning/2026-07-08-OMF-MES-개발-WBS-고객용.xlsx
@@ -611,7 +611,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08 / v0.1 (초안)</t>
+          <t>2026-07-08 / v0.2 (2026-07-10 갱신 — 기술 아키텍처·배포 방식 확정 반영)</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>기술 아키텍처·배포 방식 확정, 요구사항 우선순위 확정, 데이터 모델·API 설계 기반 수립</t>
+          <t>기술 아키텍처·배포 방식 확정(✅완료 07-10), 요구사항 우선순위 확정, 데이터 모델·API 설계 기반 수립</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t>진행 중</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t>진행 중</t>
         </is>
       </c>
     </row>

--- a/docs/planning/2026-07-08-OMF-MES-개발-WBS-고객용.xlsx
+++ b/docs/planning/2026-07-08-OMF-MES-개발-WBS-고객용.xlsx
@@ -611,7 +611,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08 / v0.2 (2026-07-10 갱신 — 기술 아키텍처·배포 방식 확정 반영)</t>
+          <t>2026-07-08 / v0.3 (2026-07-13 갱신 — 기술 아키텍처·배포 방식 확정 반영, 일정 표기 정본 정합 확인)</t>
         </is>
       </c>
     </row>
